--- a/laporan_padel_dki_jakarta_2026-09-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-22.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.040.000</t>
+          <t>Rp12.240.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.022.989</t>
+          <t>Rp5.170.989</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp2.320.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>17</v>
       </c>
       <c r="D54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp847.000</t>
+          <t>Rp698.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>144</v>
       </c>
       <c r="D59" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.198.000</t>
+          <t>Rp998.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp8.570.000</t>
+          <t>Rp7.980.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp4.320.000</t>
+          <t>Rp5.445.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>36</v>
       </c>
       <c r="D89" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp580.000</t>
+          <t>Rp630.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp243.000</t>
+          <t>Rp405.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.775.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.230.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp997.000</t>
+          <t>Rp1.645.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rp160.000 - Rp250.000</t>
+          <t>Rp110.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -4935,16 +4935,16 @@
         <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp8.350.000</t>
+          <t>Rp8.600.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.990.000</t>
+          <t>Rp2.480.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.995.000</t>
+          <t>Rp10.220.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.445.000</t>
+          <t>Rp13.595.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp8.106.000</t>
+          <t>Rp7.856.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp9.550.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.759.000</t>
+          <t>Rp6.921.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp24.925.000</t>
+          <t>Rp25.650.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.745.000</t>
+          <t>Rp5.145.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.066.000</t>
+          <t>Rp4.155.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.990.000</t>
+          <t>Rp15.830.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.480.000</t>
+          <t>Rp6.120.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.355.000</t>
+          <t>Rp3.335.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-22.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.524.000</t>
+          <t>Rp2.124.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.240.000</t>
+          <t>Rp12.420.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.750.000</t>
+          <t>Rp6.260.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp17.175.000</t>
+          <t>Rp17.880.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.983.000</t>
+          <t>Rp2.183.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.230.000</t>
+          <t>Rp6.740.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.830.000</t>
+          <t>Rp2.670.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.758.000</t>
+          <t>Rp2.538.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.184.000</t>
+          <t>Rp6.048.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>36</v>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>54</v>
       </c>
       <c r="D56" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp2.110.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>144</v>
       </c>
       <c r="D59" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp998.000</t>
+          <t>Rp1.197.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>68</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.790.000</t>
+          <t>Rp1.110.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp7.980.000</t>
+          <t>Rp8.180.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.775.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>96</v>
       </c>
       <c r="D77" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp300.000</t>
+          <t>Rp125.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2900,16 +2900,16 @@
         <v>36</v>
       </c>
       <c r="D80" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp1.606.000</t>
+          <t>Rp2.006.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>135</v>
       </c>
       <c r="D82" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp5.210.000</t>
+          <t>Rp5.435.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>96</v>
       </c>
       <c r="D83" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>36</v>
       </c>
       <c r="D84" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp1.130.000</t>
+          <t>Rp1.380.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.445.000</t>
+          <t>Rp5.695.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>34</v>
       </c>
       <c r="D92" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp3.040.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.976.124</t>
+          <t>Rp13.552.562</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rp134.824 - Rp700.000</t>
+          <t>Rp134.824 - Rp627.000</t>
         </is>
       </c>
     </row>
@@ -3571,16 +3571,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp11.100.000</t>
+          <t>Rp12.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp10.625.000</t>
+          <t>Rp10.250.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.073.000</t>
+          <t>Rp898.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.760.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.950.000</t>
+          <t>Rp7.850.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp4.230.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp2.415.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>53</v>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp7.550.000</t>
+          <t>Rp7.950.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.320.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp12.895.000</t>
+          <t>Rp13.170.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>90</v>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D45" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.900.000</t>
+          <t>Rp7.650.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5211,14 +5211,14 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D58" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp71.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp8.600.000</t>
+          <t>Rp9.800.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.470.000</t>
+          <t>Rp15.097.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp45.400.000</t>
+          <t>Rp47.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.045.000</t>
+          <t>Rp10.385.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.595.000</t>
+          <t>Rp14.550.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.325.000</t>
+          <t>Rp8.484.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.306.000</t>
+          <t>Rp4.864.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.195.000</t>
+          <t>Rp6.105.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.612.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.700.000</t>
+          <t>Rp22.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.921.000</t>
+          <t>Rp7.164.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.990.000</t>
+          <t>Rp6.440.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp8.805.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp7.925.000</t>
+          <t>Rp8.025.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.632.000</t>
+          <t>Rp3.920.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp25.650.000</t>
+          <t>Rp25.950.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp10.175.000</t>
+          <t>Rp10.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp31.050.000</t>
+          <t>Rp33.750.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.680.000</t>
+          <t>Rp6.055.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp160.000</t>
+          <t>Rp125.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7909,16 +7909,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp465.000</t>
+          <t>Rp930.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.620.000</t>
+          <t>Rp7.410.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.860.000</t>
+          <t>Rp2.345.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.060.000</t>
+          <t>Rp1.580.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp738.000</t>
+          <t>Rp1.008.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp960.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.830.000</t>
+          <t>Rp18.350.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp665.000</t>
+          <t>Rp955.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.260.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp185.000</t>
+          <t>Rp555.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.584.000</t>
+          <t>Rp1.684.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-22.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.360.000</t>
+          <t>Rp1.520.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.184.000</t>
+          <t>Rp3.776.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.878.000</t>
+          <t>Rp13.978.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.510.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.890.000</t>
+          <t>Rp22.637.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.320.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.183.000</t>
+          <t>Rp2.573.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.360.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.285.000</t>
+          <t>Rp4.665.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.740.000</t>
+          <t>Rp6.910.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.538.000</t>
+          <t>Rp2.733.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>51</v>
       </c>
       <c r="D40" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>180</v>
       </c>
       <c r="D41" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.048.000</t>
+          <t>Rp6.336.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>30</v>
       </c>
       <c r="D51" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp980.000</t>
+          <t>Rp2.260.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>36</v>
       </c>
       <c r="D53" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>17</v>
       </c>
       <c r="D54" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp698.000</t>
+          <t>Rp1.098.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.360.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>54</v>
       </c>
       <c r="D56" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.255.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp248.000</t>
+          <t>Rp397.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>144</v>
       </c>
       <c r="D59" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.197.000</t>
+          <t>Rp1.297.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>90</v>
       </c>
       <c r="D60" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp9.920.000</t>
+          <t>Rp10.360.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp196.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rp68.000 - Rp99.000</t>
+          <t>Rp49.000 - Rp68.000</t>
         </is>
       </c>
     </row>
@@ -2497,16 +2497,16 @@
         <v>34</v>
       </c>
       <c r="D67" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp1.355.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp8.180.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,21 +2838,21 @@
         <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp200.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2900,16 +2900,16 @@
         <v>36</v>
       </c>
       <c r="D80" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.006.000</t>
+          <t>Rp2.262.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>135</v>
       </c>
       <c r="D82" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp5.435.000</t>
+          <t>Rp5.885.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>36</v>
       </c>
       <c r="D84" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp1.380.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>80</v>
       </c>
       <c r="D85" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp2.090.000</t>
+          <t>Rp2.588.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.695.000</t>
+          <t>Rp6.055.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>28</v>
       </c>
       <c r="D90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp693.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>34</v>
       </c>
       <c r="D92" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp3.840.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp405.000</t>
+          <t>Rp567.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.552.562</t>
+          <t>Rp14.050.482</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.850.000</t>
+          <t>Rp9.450.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.230.000</t>
+          <t>Rp5.445.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.415.000</t>
+          <t>Rp2.805.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.870.000</t>
+          <t>Rp3.220.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>53</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp7.950.000</t>
+          <t>Rp8.350.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.320.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp13.170.000</t>
+          <t>Rp14.020.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>32</v>
       </c>
       <c r="D50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.320.000</t>
+          <t>Rp3.652.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.650.000</t>
+          <t>Rp8.050.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp71.000</t>
+          <t>Rp328.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp4.575.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>64</v>
       </c>
       <c r="D65" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp9.600.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.376.000</t>
+          <t>Rp2.970.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp7.450.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5699,16 +5699,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp8.100.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.260.000</t>
+          <t>Rp4.770.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp6.925.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.940.000</t>
+          <t>Rp10.320.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp597.000</t>
+          <t>Rp735.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp14.550.000</t>
+          <t>Rp15.135.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp16.854.000</t>
+          <t>Rp17.129.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.864.000</t>
+          <t>Rp5.980.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.105.000</t>
+          <t>Rp6.655.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp693.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.164.000</t>
+          <t>Rp6.865.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>56</v>
       </c>
       <c r="D29" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.690.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.440.000</t>
+          <t>Rp4.790.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp9.980.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp8.025.000</t>
+          <t>Rp9.325.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.920.000</t>
+          <t>Rp4.496.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp5.775.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>56</v>
       </c>
       <c r="D42" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp6.055.000</t>
+          <t>Rp6.975.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>48</v>
       </c>
       <c r="D50" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp930.000</t>
+          <t>Rp1.705.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.740.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.345.000</t>
+          <t>Rp2.495.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.580.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.145.000</t>
+          <t>Rp6.165.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.280.000</t>
+          <t>Rp3.840.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.641.000</t>
+          <t>Rp8.478.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp250.000</t>
+          <t>Rp100.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.350.000</t>
+          <t>Rp17.290.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.120.000</t>
+          <t>Rp4.755.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.680.000</t>
+          <t>Rp5.180.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp955.000</t>
+          <t>Rp1.245.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.975.000</t>
+          <t>Rp2.425.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.481.000</t>
+          <t>Rp4.871.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.650.000</t>
+          <t>Rp2.885.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp555.000</t>
+          <t>Rp895.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.684.000</t>
+          <t>Rp2.179.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.335.000</t>
+          <t>Rp4.035.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.189.000</t>
+          <t>Rp1.393.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-22.xlsx
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp6.260.000</t>
+          <t>Rp6.810.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.978.000</t>
+          <t>Rp15.078.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.868.000</t>
+          <t>Rp4.568.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.510.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.665.000</t>
+          <t>Rp5.045.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>180</v>
       </c>
       <c r="D41" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.899.000</t>
+          <t>Rp2.099.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>36</v>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.725.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>176</v>
       </c>
       <c r="D68" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.889.000</t>
+          <t>Rp4.383.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>108</v>
       </c>
       <c r="D69" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.808.000</t>
+          <t>Rp3.078.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.445.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp6.055.000</t>
+          <t>Rp5.695.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp567.000</t>
+          <t>Rp729.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.050.482</t>
+          <t>Rp14.225.482</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.970.000</t>
+          <t>Rp6.320.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>90</v>
       </c>
       <c r="D34" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp328.000</t>
+          <t>Rp399.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.025.000</t>
+          <t>Rp850.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.100.000</t>
+          <t>Rp8.450.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.770.000</t>
+          <t>Rp4.920.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp15.135.000</t>
+          <t>Rp15.410.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.900.000</t>
+          <t>Rp23.300.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp9.325.000</t>
+          <t>Rp9.525.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp10.400.000</t>
+          <t>Rp10.665.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.410.000</t>
+          <t>Rp7.870.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.840.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.008.000</t>
+          <t>Rp1.143.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.155.000</t>
+          <t>Rp2.855.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.179.000</t>
+          <t>Rp2.278.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-22.xlsx
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.170.989</t>
+          <t>Rp5.318.989</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.425.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.070.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.796.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp397.000</t>
+          <t>Rp496.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>108</v>
       </c>
       <c r="D69" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.078.000</t>
+          <t>Rp3.178.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.225.482</t>
+          <t>Rp14.795.482</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.775.000</t>
+          <t>Rp7.175.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp8.050.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp9.850.000</t>
+          <t>Rp10.350.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp7.450.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.920.000</t>
+          <t>Rp4.770.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp735.000</t>
+          <t>Rp1.041.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp15.410.000</t>
+          <t>Rp16.235.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.484.000</t>
+          <t>Rp8.734.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp5.825.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp2.108.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.775.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp25.950.000</t>
+          <t>Rp26.150.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp6.975.000</t>
+          <t>Rp7.325.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.705.000</t>
+          <t>Rp1.860.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.495.000</t>
+          <t>Rp2.645.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp5.775.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.035.000</t>
+          <t>Rp3.735.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
